--- a/Data/Table1_raw.xlsx
+++ b/Data/Table1_raw.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/connorpiercy/Documents/GitHub/Group_8_Project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/connorpiercy/Documents/GitHub/Group_8_Project/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AB5F282-5569-3C40-AFDF-6CF1509766A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A29337-2311-3C4D-916B-CFF360D1FBCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13620" yWindow="640" windowWidth="14820" windowHeight="16660" xr2:uid="{D913AFE5-FFEF-D343-BAB9-A12C62385E55}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="56">
   <si>
     <t>11-Na*</t>
   </si>
@@ -204,6 +204,9 @@
   </si>
   <si>
     <t>[0.00]</t>
+  </si>
+  <si>
+    <t>Elements</t>
   </si>
 </sst>
 </file>
@@ -245,13 +248,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -589,56 +591,59 @@
   <dimension ref="A1:R36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>55</v>
+      </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
     </row>
